--- a/output/pdf_financials_xlsx/OTMC.xlsx
+++ b/output/pdf_financials_xlsx/OTMC.xlsx
@@ -1285,31 +1285,31 @@
         <v>-0.498475</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.007349</v>
+        <v>-1.007349</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.443894</v>
+        <v>-0.443894</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1.622017</v>
+        <v>-1.622017</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>2.247025</v>
+        <v>-2.247025</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.352354</v>
+        <v>-0.352354</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1.27537</v>
+        <v>-1.27537</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>2.704053</v>
+        <v>-2.704053</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.828333</v>
+        <v>-0.828333</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.443421</v>
+        <v>-0.443421</v>
       </c>
     </row>
     <row r="17">
@@ -1585,31 +1585,31 @@
         <v>-0.498475</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.007349</v>
+        <v>-1.007349</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.443894</v>
+        <v>-0.443894</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>1.622017</v>
+        <v>-1.622017</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.247025</v>
+        <v>-2.247025</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.352354</v>
+        <v>-0.352354</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>1.27537</v>
+        <v>-1.27537</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>2.704053</v>
+        <v>-2.704053</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.828333</v>
+        <v>-0.828333</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.443421</v>
+        <v>-0.443421</v>
       </c>
     </row>
     <row r="21">
@@ -1759,31 +1759,31 @@
         <v>-0.498475</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.007349</v>
+        <v>-1.007349</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.443894</v>
+        <v>-0.443894</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>1.622017</v>
+        <v>-1.622017</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>2.247025</v>
+        <v>-2.247025</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.352354</v>
+        <v>-0.352354</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1.27537</v>
+        <v>-1.27537</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>2.704053</v>
+        <v>-2.704053</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>0.828333</v>
+        <v>-0.828333</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>0.443421</v>
+        <v>-0.443421</v>
       </c>
     </row>
     <row r="24">
@@ -2023,31 +2023,31 @@
         <v>-0.498475</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.007349</v>
+        <v>-1.007349</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.443894</v>
+        <v>-0.443894</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.622017</v>
+        <v>-1.622017</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.247025</v>
+        <v>-2.247025</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.352354</v>
+        <v>-0.352354</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1.27537</v>
+        <v>-1.27537</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>2.704053</v>
+        <v>-2.704053</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.828333</v>
+        <v>-0.828333</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>0.443421</v>
+        <v>-0.443421</v>
       </c>
     </row>
     <row r="28">
@@ -2139,31 +2139,31 @@
         <v>-0.498475</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.007349</v>
+        <v>-1.007349</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.443894</v>
+        <v>-0.443894</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.622017</v>
+        <v>-1.622017</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.247025</v>
+        <v>-2.247025</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.352354</v>
+        <v>-0.352354</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1.27537</v>
+        <v>-1.27537</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.704053</v>
+        <v>-2.704053</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.828333</v>
+        <v>-0.828333</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>0.443421</v>
+        <v>-0.443421</v>
       </c>
     </row>
     <row r="30">
@@ -2289,31 +2289,31 @@
         <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -7357,10 +7357,10 @@
         <v>1.925</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-1.026729</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.362871</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0</v>
@@ -26705,7 +26705,11 @@
           <t>Deferred exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -31142,31 +31146,31 @@
         </is>
       </c>
       <c r="M235" s="5" t="n">
-        <v>1.007349</v>
+        <v>-1.007349</v>
       </c>
       <c r="N235" s="5" t="n">
-        <v>0.443894</v>
+        <v>-0.443894</v>
       </c>
       <c r="O235" s="5" t="n">
-        <v>1.622017</v>
+        <v>-1.622017</v>
       </c>
       <c r="P235" s="5" t="n">
-        <v>2.247025</v>
+        <v>-2.247025</v>
       </c>
       <c r="Q235" s="5" t="n">
-        <v>0.352354</v>
+        <v>-0.352354</v>
       </c>
       <c r="R235" s="5" t="n">
-        <v>1.27537</v>
+        <v>-1.27537</v>
       </c>
       <c r="S235" s="5" t="n">
-        <v>2.704053</v>
+        <v>-2.704053</v>
       </c>
       <c r="T235" s="5" t="n">
-        <v>0.828333</v>
+        <v>-0.828333</v>
       </c>
       <c r="U235" s="5" t="n">
-        <v>0.443421</v>
+        <v>-0.443421</v>
       </c>
     </row>
     <row r="236">

--- a/output/pdf_financials_xlsx/OTMC.xlsx
+++ b/output/pdf_financials_xlsx/OTMC.xlsx
@@ -1029,55 +1029,55 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.040768</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.012748</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.024523</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.045565</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.026255</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.017816</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.009913</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.003681</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001875</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001204</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007207</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005871</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000879</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003548</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.024681</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000855</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-8.1e-05</v>
       </c>
     </row>
     <row r="13">
@@ -1999,55 +1999,55 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.946478</v>
+        <v>-1.987246</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.807744</v>
+        <v>-0.820492</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.076908</v>
+        <v>-1.101431</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.099345</v>
+        <v>-1.14491</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.7680439999999999</v>
+        <v>-0.794299</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.990035</v>
+        <v>-1.007851</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.547937</v>
+        <v>-0.55785</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.498475</v>
+        <v>-0.502156</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.007349</v>
+        <v>-1.005474</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.443894</v>
+        <v>-0.44269</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.622017</v>
+        <v>-1.61481</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.247025</v>
+        <v>-2.241154</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.352354</v>
+        <v>-0.351475</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.27537</v>
+        <v>-1.271822</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.704053</v>
+        <v>-2.679372</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.828333</v>
+        <v>-0.827478</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.443421</v>
+        <v>-0.44334</v>
       </c>
     </row>
     <row r="28">
@@ -2115,55 +2115,55 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.946478</v>
+        <v>-1.987246</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.807744</v>
+        <v>-0.820492</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.076908</v>
+        <v>-1.101431</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.099345</v>
+        <v>-1.14491</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.7680439999999999</v>
+        <v>-0.794299</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.990035</v>
+        <v>-1.007851</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.547937</v>
+        <v>-0.55785</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.498475</v>
+        <v>-0.502156</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.007349</v>
+        <v>-1.005474</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.443894</v>
+        <v>-0.44269</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.622017</v>
+        <v>-1.61481</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.247025</v>
+        <v>-2.241154</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.352354</v>
+        <v>-0.351475</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.27537</v>
+        <v>-1.271822</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.704053</v>
+        <v>-2.679372</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.828333</v>
+        <v>-0.827478</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.443421</v>
+        <v>-0.44334</v>
       </c>
     </row>
     <row r="30">
@@ -30914,7 +30914,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -37158,7 +37158,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E297" s="5" t="n">

--- a/output/pdf_financials_xlsx/OTMC.xlsx
+++ b/output/pdf_financials_xlsx/OTMC.xlsx
@@ -1261,19 +1261,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-1.946478</v>
+        <v>-2.038118</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.807744</v>
+        <v>-0.350244</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-1.076908</v>
+        <v>-0.251407</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-1.099345</v>
+        <v>-1.726103</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.7680439999999999</v>
+        <v>-0.300344</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-0.990035</v>
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>0.09164</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.4575</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.825501</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>0.626758</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.4677</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -1999,19 +1999,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.987246</v>
+        <v>-2.078886</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.820492</v>
+        <v>-0.362992</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.101431</v>
+        <v>-0.27593</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.14491</v>
+        <v>-1.771668</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.794299</v>
+        <v>-0.326599</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-1.007851</v>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.987246</v>
+        <v>-2.078886</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.820492</v>
+        <v>-0.362992</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.101431</v>
+        <v>-0.27593</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.14491</v>
+        <v>-1.771668</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.794299</v>
+        <v>-0.326599</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-1.007851</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-4.496304924445003</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-130.623222667626</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-328.3524325098346</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-36.31057938025715</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0</v>
+        <v>-155.7214394161362</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -4581,22 +4581,22 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.017649</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.020714</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.013557</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.058207</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.065745</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.041977</v>
       </c>
     </row>
     <row r="71">
@@ -4639,22 +4639,22 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.017649</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.020714</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.013557</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.058207</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.065745</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>0.041977</v>
       </c>
     </row>
     <row r="72">
@@ -4871,22 +4871,22 @@
         <v>0.682338</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.759051</v>
+        <v>0.741402</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>1.068822</v>
+        <v>1.048108</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>1.002093</v>
+        <v>0.988536</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.888502</v>
+        <v>0.830295</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>1.049815</v>
+        <v>0.98407</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>1.310898</v>
+        <v>1.268921</v>
       </c>
     </row>
     <row r="76">
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>0</v>
+        <v>0.034271</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0</v>
+        <v>0.013557</v>
       </c>
       <c r="O78" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>0</v>
+        <v>0.107723</v>
       </c>
       <c r="Q78" s="3" t="n">
         <v>0</v>
@@ -5115,16 +5115,16 @@
         <v>0</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>0</v>
+        <v>0.034271</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>0</v>
+        <v>0.013557</v>
       </c>
       <c r="O79" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>0</v>
+        <v>0.107723</v>
       </c>
       <c r="Q79" s="3" t="n">
         <v>0</v>
@@ -5194,35 +5194,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M80" s="3" t="n">
+        <v>0.02491287451482993</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.01263757294878669</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.005382059958934847</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0.7508620455594472</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>-0.06642264381217178</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>-0.03220614016579906</v>
       </c>
     </row>
     <row r="81">
@@ -5497,16 +5485,16 @@
         <v>0</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>0.034271</v>
+        <v>0</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>0.013557</v>
+        <v>0</v>
       </c>
       <c r="O85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>0.107723</v>
+        <v>0</v>
       </c>
       <c r="Q85" s="3" t="n">
         <v>0.041977</v>
@@ -9301,7 +9289,11 @@
           <t>Current portion of lease obligations 7</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -11687,7 +11679,11 @@
           <t>Current portion of lease obligations 8 65,745</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -11992,7 +11988,11 @@
           <t>Lease obligations 8 41,977</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -13330,7 +13330,11 @@
           <t>Current portion of lease obligations (note 7)</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -13522,7 +13526,11 @@
           <t>Lease obligations (note 7)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -14456,7 +14464,11 @@
           <t>Current portion of lease obligations</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -29008,7 +29020,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E213" s="5" t="n">
         <v>0.091639</v>
       </c>
@@ -37352,7 +37368,11 @@
           <t>Deferred income tax recovery (expense) (note 8)</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -37942,7 +37962,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -38538,7 +38562,11 @@
           <t>Deferred income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -38835,7 +38863,11 @@
           <t>Future income tax recovery (note 6)</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -39433,7 +39465,11 @@
           <t>Future income tax (recovery)(note 6)</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E320" s="5" t="n">
         <v>-0.09164</v>
       </c>
